--- a/examples/results_20260812.xlsx
+++ b/examples/results_20260812.xlsx
@@ -1030,12 +1030,13 @@
       </c>
       <c r="K4" s="14" t="inlineStr">
         <is>
-          <t>フォームの入力欄に Tab キーで移動し、テキストを入力した</t>
+          <t>キーボード操作でナビゲーションリンクにフォーカスを移動し、Enter キーで選択した</t>
         </is>
       </c>
       <c r="L4" s="14" t="inlineStr">
         <is>
-          <t>入力欄に移動するとラベルが読み上げられ、テキストを入力できた</t>
+          <t>リンクにフォーカスが当たったことが視覚的に確認でき、Enter キーで遷移できた。
+なお、フォーカスインジケータが明瞭に表示された。</t>
         </is>
       </c>
       <c r="M4" s="7" t="inlineStr">
@@ -1351,12 +1352,14 @@
       </c>
       <c r="K7" s="14" t="inlineStr">
         <is>
-          <t>フォームの入力欄に Tab キーで移動し、テキストを入力した</t>
+          <t>矢印キーを押してテーブル内に移動した。
+続けて下矢印キーで各セルを移動した。</t>
         </is>
       </c>
       <c r="L7" s="14" t="inlineStr">
         <is>
-          <t>入力欄に移動するとラベルが読み上げられ、テキストを入力できた</t>
+          <t>テーブルに入ると「テーブル」と読み上げられ、セル間を矢印キーで移動できた。
+行見出しも読み上げられ、どの行のセルかを識別できた。</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
@@ -1672,12 +1675,14 @@
       </c>
       <c r="K10" s="14" t="inlineStr">
         <is>
-          <t>フォームの入力欄に Tab キーで移動し、テキストを入力した</t>
+          <t>フォームの入力欄に Tab キーで移動した。
+ラベルを読み上げさせ、テキストを入力した。</t>
         </is>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>入力欄に移動するとラベルが読み上げられ、テキストを入力できた</t>
+          <t>入力欄に移動するとラベルが読み上げられ、テキストを入力できた。
+入力内容も読み上げられ、正しく入力されていることが確認できた。</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
